--- a/AtchisonRegime/Outputs/USA/USA_Momentum/df_regSummary_USA_Momentum.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Momentum/df_regSummary_USA_Momentum.xlsx
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.852079742450122</v>
+        <v>1.581408455357284</v>
       </c>
       <c r="H2" t="n">
-        <v>3.93481658177471</v>
+        <v>4.393631911096492</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.747234236335339</v>
+        <v>-13.3055123347488</v>
       </c>
       <c r="J2" t="n">
         <v>11.7483945325047</v>
       </c>
       <c r="K2" t="n">
-        <v>38.73239436619718</v>
+        <v>39.16083916083916</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2290583342417606</v>
+        <v>0.1888311571191753</v>
       </c>
       <c r="O2" t="n">
         <v>-0.01023538750965192</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5116733617813327</v>
+        <v>0.3928046843520732</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>7.42189952260202</v>
       </c>
       <c r="K3" t="n">
-        <v>18.30985915492958</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>8.541253775102129</v>
       </c>
       <c r="K4" t="n">
-        <v>20.42253521126761</v>
+        <v>20.27972027972028</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>13.1224591254952</v>
       </c>
       <c r="K5" t="n">
-        <v>22.53521126760564</v>
+        <v>22.37762237762238</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
